--- a/output/pdf_financials_xlsx/KEL.xlsx
+++ b/output/pdf_financials_xlsx/KEL.xlsx
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001095</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000938</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.140175</v>
+        <v>-0.141113</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-141.039</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.055757</v>
+        <v>-0.056695</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-141.039</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-29.93535848124644</v>
+        <v>-30.43896101107066</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-87.98824652355374</v>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.032015</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.032015</v>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.033957</v>
@@ -37394,7 +37394,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E358" s="5" t="n">
@@ -68232,7 +68232,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">

--- a/output/pdf_financials_xlsx/KEL.xlsx
+++ b/output/pdf_financials_xlsx/KEL.xlsx
@@ -6050,43 +6050,43 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.003235</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.002883</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>9.896000000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-12.546</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>8.723000000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-17.699</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>2.392</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>1.903</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-17.77</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>11.562</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-7.797</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>6.079</v>
       </c>
     </row>
     <row r="107">
@@ -38318,7 +38318,11 @@
           <t>Deferred income tax expense [11]</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -38486,7 +38490,11 @@
           <t>Change in non-cash operating working capital [16]</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -40238,7 +40246,11 @@
           <t>Deferred income tax expense [12]</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -40398,7 +40410,11 @@
           <t>Change in non-cash operating working capital [17]</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -43318,7 +43334,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -43476,7 +43496,11 @@
           <t>Change in non-cash operating working capital [18]</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -45130,7 +45154,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -45210,7 +45238,11 @@
           <t>Change in non-cash operating working capital [19]</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -47556,7 +47588,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -48658,7 +48694,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -48912,7 +48952,11 @@
           <t>Change in non-cash operating working capital [18]</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -50022,7 +50066,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -50190,7 +50238,11 @@
           <t>Change in non-cash operating working capital [16]</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -51808,7 +51860,11 @@
           <t>Change in non-cash operating working capital [15]</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
